--- a/artfynd/A 18029-2022 artfynd.xlsx
+++ b/artfynd/A 18029-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18029-2022 artfynd.xlsx
+++ b/artfynd/A 18029-2022 artfynd.xlsx
@@ -2237,10 +2237,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118305359</v>
+        <v>118305354</v>
       </c>
       <c r="B15" t="n">
-        <v>100107</v>
+        <v>94143</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>2779</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484799</v>
+        <v>484620</v>
       </c>
       <c r="R15" t="n">
-        <v>6473280</v>
+        <v>6473484</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118305354</v>
+        <v>118305359</v>
       </c>
       <c r="B16" t="n">
-        <v>94143</v>
+        <v>100107</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2359,21 +2359,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2779</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484620</v>
+        <v>484799</v>
       </c>
       <c r="R16" t="n">
-        <v>6473484</v>
+        <v>6473280</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -4463,10 +4463,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118305367</v>
+        <v>118305340</v>
       </c>
       <c r="B36" t="n">
-        <v>104853</v>
+        <v>106855</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4475,30 +4475,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221141</v>
+        <v>220103</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485042</v>
+        <v>484688</v>
       </c>
       <c r="R36" t="n">
-        <v>6473417</v>
+        <v>6473379</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4537,12 +4537,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4569,10 +4569,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118305340</v>
+        <v>118305367</v>
       </c>
       <c r="B37" t="n">
-        <v>106855</v>
+        <v>104853</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4581,30 +4581,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220103</v>
+        <v>221141</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>484688</v>
+        <v>485042</v>
       </c>
       <c r="R37" t="n">
-        <v>6473379</v>
+        <v>6473417</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4643,12 +4643,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5417,10 +5417,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118305342</v>
+        <v>118305321</v>
       </c>
       <c r="B45" t="n">
-        <v>57993</v>
+        <v>109963</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5429,25 +5429,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103055</v>
+        <v>219711</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>485057</v>
+        <v>484640</v>
       </c>
       <c r="R45" t="n">
-        <v>6473346</v>
+        <v>6473534</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5523,10 +5523,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118305321</v>
+        <v>118305342</v>
       </c>
       <c r="B46" t="n">
-        <v>109963</v>
+        <v>57993</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5535,25 +5535,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219711</v>
+        <v>103055</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>484640</v>
+        <v>485057</v>
       </c>
       <c r="R46" t="n">
-        <v>6473534</v>
+        <v>6473346</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5597,12 +5597,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6265,10 +6265,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118305374</v>
+        <v>118305377</v>
       </c>
       <c r="B53" t="n">
-        <v>104853</v>
+        <v>100107</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6281,26 +6281,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>485099</v>
+        <v>485117</v>
       </c>
       <c r="R53" t="n">
-        <v>6473500</v>
+        <v>6473448</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118305377</v>
+        <v>118305315</v>
       </c>
       <c r="B54" t="n">
         <v>100107</v>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6415,10 +6415,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>485117</v>
+        <v>484915</v>
       </c>
       <c r="R54" t="n">
-        <v>6473448</v>
+        <v>6473291</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6445,12 +6445,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6477,10 +6477,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118305315</v>
+        <v>118305311</v>
       </c>
       <c r="B55" t="n">
-        <v>100107</v>
+        <v>105495</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6489,25 +6489,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>484915</v>
+        <v>484912</v>
       </c>
       <c r="R55" t="n">
-        <v>6473291</v>
+        <v>6473377</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6583,10 +6583,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118305311</v>
+        <v>118305374</v>
       </c>
       <c r="B56" t="n">
-        <v>105495</v>
+        <v>104853</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6595,20 +6595,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220785</v>
+        <v>221141</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6627,10 +6627,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>484912</v>
+        <v>485099</v>
       </c>
       <c r="R56" t="n">
-        <v>6473377</v>
+        <v>6473500</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 18029-2022 artfynd.xlsx
+++ b/artfynd/A 18029-2022 artfynd.xlsx
@@ -4039,10 +4039,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118305334</v>
+        <v>118305361</v>
       </c>
       <c r="B32" t="n">
-        <v>108505</v>
+        <v>100107</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4051,30 +4051,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220228</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>484663</v>
+        <v>484933</v>
       </c>
       <c r="R32" t="n">
-        <v>6473423</v>
+        <v>6473262</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4113,12 +4113,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4145,7 +4145,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118305361</v>
+        <v>118305366</v>
       </c>
       <c r="B33" t="n">
         <v>100107</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>484933</v>
+        <v>485044</v>
       </c>
       <c r="R33" t="n">
-        <v>6473262</v>
+        <v>6473454</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4251,10 +4251,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118305366</v>
+        <v>118305334</v>
       </c>
       <c r="B34" t="n">
-        <v>100107</v>
+        <v>108505</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4263,30 +4263,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>220228</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485044</v>
+        <v>484663</v>
       </c>
       <c r="R34" t="n">
-        <v>6473454</v>
+        <v>6473423</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4325,12 +4325,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 18029-2022 artfynd.xlsx
+++ b/artfynd/A 18029-2022 artfynd.xlsx
@@ -1919,10 +1919,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118305319</v>
+        <v>118305329</v>
       </c>
       <c r="B12" t="n">
-        <v>106776</v>
+        <v>108505</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1935,26 +1935,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220079</v>
+        <v>220228</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484611</v>
+        <v>484656</v>
       </c>
       <c r="R12" t="n">
-        <v>6473524</v>
+        <v>6473428</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2025,10 +2025,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118305325</v>
+        <v>118305323</v>
       </c>
       <c r="B13" t="n">
-        <v>104853</v>
+        <v>100107</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2041,21 +2041,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484794</v>
+        <v>484694</v>
       </c>
       <c r="R13" t="n">
-        <v>6473389</v>
+        <v>6473459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118305373</v>
+        <v>118305375</v>
       </c>
       <c r="B14" t="n">
         <v>100107</v>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485104</v>
+        <v>485094</v>
       </c>
       <c r="R14" t="n">
-        <v>6473496</v>
+        <v>6473498</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118305354</v>
+        <v>118305380</v>
       </c>
       <c r="B15" t="n">
-        <v>94143</v>
+        <v>104853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2253,26 +2253,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2779</v>
+        <v>221141</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484620</v>
+        <v>485114</v>
       </c>
       <c r="R15" t="n">
-        <v>6473484</v>
+        <v>6473403</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118305359</v>
+        <v>118305360</v>
       </c>
       <c r="B16" t="n">
-        <v>100107</v>
+        <v>104853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2359,21 +2359,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484799</v>
+        <v>484788</v>
       </c>
       <c r="R16" t="n">
-        <v>6473280</v>
+        <v>6473281</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118305351</v>
+        <v>118305326</v>
       </c>
       <c r="B17" t="n">
-        <v>57623</v>
+        <v>104853</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2461,25 +2461,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103008</v>
+        <v>221141</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485011</v>
+        <v>484805</v>
       </c>
       <c r="R17" t="n">
-        <v>6473395</v>
+        <v>6473426</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2523,12 +2523,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2555,10 +2555,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118305333</v>
+        <v>118305369</v>
       </c>
       <c r="B18" t="n">
-        <v>106776</v>
+        <v>100107</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2567,30 +2567,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220079</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484662</v>
+        <v>485043</v>
       </c>
       <c r="R18" t="n">
-        <v>6473426</v>
+        <v>6473421</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2629,12 +2629,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2661,7 +2661,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118305381</v>
+        <v>118305366</v>
       </c>
       <c r="B19" t="n">
         <v>100107</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>485107</v>
+        <v>485044</v>
       </c>
       <c r="R19" t="n">
-        <v>6473466</v>
+        <v>6473454</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2767,10 +2767,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118305318</v>
+        <v>118305377</v>
       </c>
       <c r="B20" t="n">
-        <v>102758</v>
+        <v>100107</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2783,26 +2783,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>484764</v>
+        <v>485117</v>
       </c>
       <c r="R20" t="n">
-        <v>6473594</v>
+        <v>6473448</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,10 +2873,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118305348</v>
+        <v>118305363</v>
       </c>
       <c r="B21" t="n">
-        <v>57933</v>
+        <v>100107</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2885,25 +2885,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103042</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>484666</v>
+        <v>484973</v>
       </c>
       <c r="R21" t="n">
-        <v>6473631</v>
+        <v>6473286</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2947,12 +2947,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,7 +2979,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118305332</v>
+        <v>118305334</v>
       </c>
       <c r="B22" t="n">
         <v>108505</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>484606</v>
+        <v>484663</v>
       </c>
       <c r="R22" t="n">
-        <v>6473524</v>
+        <v>6473423</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3085,10 +3085,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118305355</v>
+        <v>118305317</v>
       </c>
       <c r="B23" t="n">
-        <v>100107</v>
+        <v>109963</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3101,26 +3101,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>484703</v>
+        <v>484848</v>
       </c>
       <c r="R23" t="n">
-        <v>6473370</v>
+        <v>6473423</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3159,12 +3159,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3297,7 +3297,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118305363</v>
+        <v>118305361</v>
       </c>
       <c r="B25" t="n">
         <v>100107</v>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>484973</v>
+        <v>484933</v>
       </c>
       <c r="R25" t="n">
-        <v>6473286</v>
+        <v>6473262</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3403,10 +3403,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118305364</v>
+        <v>118305351</v>
       </c>
       <c r="B26" t="n">
-        <v>104853</v>
+        <v>57623</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3415,25 +3415,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221141</v>
+        <v>103008</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>484966</v>
+        <v>485011</v>
       </c>
       <c r="R26" t="n">
-        <v>6473283</v>
+        <v>6473395</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3509,10 +3509,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118305379</v>
+        <v>118305333</v>
       </c>
       <c r="B27" t="n">
-        <v>104853</v>
+        <v>106776</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3521,30 +3521,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221141</v>
+        <v>220079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>485111</v>
+        <v>484662</v>
       </c>
       <c r="R27" t="n">
-        <v>6473414</v>
+        <v>6473426</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3583,12 +3583,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3615,10 +3615,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118305326</v>
+        <v>118305311</v>
       </c>
       <c r="B28" t="n">
-        <v>104853</v>
+        <v>105495</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3627,20 +3627,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>484805</v>
+        <v>484912</v>
       </c>
       <c r="R28" t="n">
-        <v>6473426</v>
+        <v>6473377</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118305320</v>
+        <v>118305355</v>
       </c>
       <c r="B29" t="n">
-        <v>109963</v>
+        <v>100107</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3737,21 +3737,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>484737</v>
+        <v>484703</v>
       </c>
       <c r="R29" t="n">
-        <v>6473599</v>
+        <v>6473370</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3795,12 +3795,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3827,10 +3827,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118305380</v>
+        <v>118305342</v>
       </c>
       <c r="B30" t="n">
-        <v>104853</v>
+        <v>57993</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3839,30 +3839,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221141</v>
+        <v>103055</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>485114</v>
+        <v>485057</v>
       </c>
       <c r="R30" t="n">
-        <v>6473403</v>
+        <v>6473346</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3901,12 +3901,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3933,7 +3933,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118305322</v>
+        <v>118305364</v>
       </c>
       <c r="B31" t="n">
         <v>104853</v>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>484760</v>
+        <v>484966</v>
       </c>
       <c r="R31" t="n">
-        <v>6473457</v>
+        <v>6473283</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4007,12 +4007,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4039,10 +4039,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118305361</v>
+        <v>118305340</v>
       </c>
       <c r="B32" t="n">
-        <v>100107</v>
+        <v>106855</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4051,30 +4051,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>220103</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>484933</v>
+        <v>484688</v>
       </c>
       <c r="R32" t="n">
-        <v>6473262</v>
+        <v>6473379</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4113,12 +4113,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4145,10 +4145,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118305366</v>
+        <v>118305368</v>
       </c>
       <c r="B33" t="n">
-        <v>100107</v>
+        <v>57993</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4157,25 +4157,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>103055</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>485044</v>
+        <v>485047</v>
       </c>
       <c r="R33" t="n">
-        <v>6473454</v>
+        <v>6473424</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4251,10 +4251,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118305334</v>
+        <v>118305376</v>
       </c>
       <c r="B34" t="n">
-        <v>108505</v>
+        <v>104853</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4263,20 +4263,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220228</v>
+        <v>221141</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>484663</v>
+        <v>485097</v>
       </c>
       <c r="R34" t="n">
-        <v>6473423</v>
+        <v>6473479</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4325,12 +4325,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4357,7 +4357,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118305360</v>
+        <v>118305325</v>
       </c>
       <c r="B35" t="n">
         <v>104853</v>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>484788</v>
+        <v>484794</v>
       </c>
       <c r="R35" t="n">
-        <v>6473281</v>
+        <v>6473389</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4431,12 +4431,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4463,10 +4463,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118305340</v>
+        <v>118305367</v>
       </c>
       <c r="B36" t="n">
-        <v>106855</v>
+        <v>104853</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4475,30 +4475,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220103</v>
+        <v>221141</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>484688</v>
+        <v>485042</v>
       </c>
       <c r="R36" t="n">
-        <v>6473379</v>
+        <v>6473417</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4537,12 +4537,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4569,10 +4569,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118305367</v>
+        <v>118305320</v>
       </c>
       <c r="B37" t="n">
-        <v>104853</v>
+        <v>109963</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4585,16 +4585,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221141</v>
+        <v>219711</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>485042</v>
+        <v>484737</v>
       </c>
       <c r="R37" t="n">
-        <v>6473417</v>
+        <v>6473599</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4643,12 +4643,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4675,10 +4675,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118305368</v>
+        <v>118305339</v>
       </c>
       <c r="B38" t="n">
-        <v>57993</v>
+        <v>57287</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4687,20 +4687,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103055</v>
+        <v>102119</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>485047</v>
+        <v>485081</v>
       </c>
       <c r="R38" t="n">
-        <v>6473424</v>
+        <v>6473386</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4749,12 +4749,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4781,10 +4781,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118305335</v>
+        <v>118305319</v>
       </c>
       <c r="B39" t="n">
-        <v>106855</v>
+        <v>106776</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4797,26 +4797,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220103</v>
+        <v>220079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>484733</v>
+        <v>484611</v>
       </c>
       <c r="R39" t="n">
-        <v>6473319</v>
+        <v>6473524</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4887,10 +4887,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118305323</v>
+        <v>118305322</v>
       </c>
       <c r="B40" t="n">
-        <v>100107</v>
+        <v>104853</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4903,21 +4903,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>484694</v>
+        <v>484760</v>
       </c>
       <c r="R40" t="n">
-        <v>6473459</v>
+        <v>6473457</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4993,10 +4993,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118305369</v>
+        <v>118305371</v>
       </c>
       <c r="B41" t="n">
-        <v>100107</v>
+        <v>104853</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5009,26 +5009,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>485043</v>
+        <v>485082</v>
       </c>
       <c r="R41" t="n">
-        <v>6473421</v>
+        <v>6473404</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5099,10 +5099,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118305343</v>
+        <v>118305313</v>
       </c>
       <c r="B42" t="n">
-        <v>57933</v>
+        <v>100107</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5111,25 +5111,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103042</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>485042</v>
+        <v>484918</v>
       </c>
       <c r="R42" t="n">
-        <v>6473338</v>
+        <v>6473370</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5205,7 +5205,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118305362</v>
+        <v>118305381</v>
       </c>
       <c r="B43" t="n">
         <v>100107</v>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>484972</v>
+        <v>485107</v>
       </c>
       <c r="R43" t="n">
-        <v>6473266</v>
+        <v>6473466</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118305330</v>
+        <v>118305372</v>
       </c>
       <c r="B44" t="n">
-        <v>106855</v>
+        <v>104853</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5323,30 +5323,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220103</v>
+        <v>221141</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>484759</v>
+        <v>485107</v>
       </c>
       <c r="R44" t="n">
-        <v>6473331</v>
+        <v>6473491</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5385,12 +5385,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5417,10 +5417,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118305321</v>
+        <v>118305379</v>
       </c>
       <c r="B45" t="n">
-        <v>109963</v>
+        <v>104853</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5433,16 +5433,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219711</v>
+        <v>221141</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>484640</v>
+        <v>485111</v>
       </c>
       <c r="R45" t="n">
-        <v>6473534</v>
+        <v>6473414</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5523,10 +5523,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118305342</v>
+        <v>118305348</v>
       </c>
       <c r="B46" t="n">
-        <v>57993</v>
+        <v>57933</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5535,25 +5535,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103055</v>
+        <v>103042</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>485057</v>
+        <v>484666</v>
       </c>
       <c r="R46" t="n">
-        <v>6473346</v>
+        <v>6473631</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5597,12 +5597,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5629,10 +5629,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118305378</v>
+        <v>118305335</v>
       </c>
       <c r="B47" t="n">
-        <v>100107</v>
+        <v>106855</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5641,30 +5641,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>220103</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>485117</v>
+        <v>484733</v>
       </c>
       <c r="R47" t="n">
-        <v>6473432</v>
+        <v>6473319</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5703,12 +5703,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5735,10 +5735,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118305339</v>
+        <v>118305373</v>
       </c>
       <c r="B48" t="n">
-        <v>57287</v>
+        <v>100107</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5751,21 +5751,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102119</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>485081</v>
+        <v>485104</v>
       </c>
       <c r="R48" t="n">
-        <v>6473386</v>
+        <v>6473496</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5841,10 +5841,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118305317</v>
+        <v>118305362</v>
       </c>
       <c r="B49" t="n">
-        <v>109963</v>
+        <v>100107</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5857,26 +5857,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>484848</v>
+        <v>484972</v>
       </c>
       <c r="R49" t="n">
-        <v>6473423</v>
+        <v>6473266</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5915,12 +5915,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5947,10 +5947,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118305313</v>
+        <v>118305318</v>
       </c>
       <c r="B50" t="n">
-        <v>100107</v>
+        <v>102758</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5963,21 +5963,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>484918</v>
+        <v>484764</v>
       </c>
       <c r="R50" t="n">
-        <v>6473370</v>
+        <v>6473594</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6021,12 +6021,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6053,10 +6053,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118305376</v>
+        <v>118305378</v>
       </c>
       <c r="B51" t="n">
-        <v>104853</v>
+        <v>100107</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6069,21 +6069,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6097,10 +6097,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>485097</v>
+        <v>485117</v>
       </c>
       <c r="R51" t="n">
-        <v>6473479</v>
+        <v>6473432</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6159,7 +6159,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118305372</v>
+        <v>118305374</v>
       </c>
       <c r="B52" t="n">
         <v>104853</v>
@@ -6203,10 +6203,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>485107</v>
+        <v>485099</v>
       </c>
       <c r="R52" t="n">
-        <v>6473491</v>
+        <v>6473500</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6265,10 +6265,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118305377</v>
+        <v>118305321</v>
       </c>
       <c r="B53" t="n">
-        <v>100107</v>
+        <v>109963</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6281,26 +6281,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>485117</v>
+        <v>484640</v>
       </c>
       <c r="R53" t="n">
-        <v>6473448</v>
+        <v>6473534</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6339,12 +6339,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6371,7 +6371,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118305315</v>
+        <v>118305359</v>
       </c>
       <c r="B54" t="n">
         <v>100107</v>
@@ -6415,10 +6415,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>484915</v>
+        <v>484799</v>
       </c>
       <c r="R54" t="n">
-        <v>6473291</v>
+        <v>6473280</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6445,12 +6445,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6477,10 +6477,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118305311</v>
+        <v>118305332</v>
       </c>
       <c r="B55" t="n">
-        <v>105495</v>
+        <v>108505</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6489,20 +6489,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220785</v>
+        <v>220228</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>484912</v>
+        <v>484606</v>
       </c>
       <c r="R55" t="n">
-        <v>6473377</v>
+        <v>6473524</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6583,10 +6583,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118305374</v>
+        <v>118305354</v>
       </c>
       <c r="B56" t="n">
-        <v>104853</v>
+        <v>94143</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6599,21 +6599,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221141</v>
+        <v>2779</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6627,10 +6627,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>485099</v>
+        <v>484620</v>
       </c>
       <c r="R56" t="n">
-        <v>6473500</v>
+        <v>6473484</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6689,10 +6689,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118305329</v>
+        <v>118305343</v>
       </c>
       <c r="B57" t="n">
-        <v>108505</v>
+        <v>57933</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6701,30 +6701,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220228</v>
+        <v>103042</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>484656</v>
+        <v>485042</v>
       </c>
       <c r="R57" t="n">
-        <v>6473428</v>
+        <v>6473338</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6795,10 +6795,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118305371</v>
+        <v>118305315</v>
       </c>
       <c r="B58" t="n">
-        <v>104853</v>
+        <v>100107</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6811,26 +6811,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6839,10 +6839,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485082</v>
+        <v>484915</v>
       </c>
       <c r="R58" t="n">
-        <v>6473404</v>
+        <v>6473291</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6901,10 +6901,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118305375</v>
+        <v>118305330</v>
       </c>
       <c r="B59" t="n">
-        <v>100107</v>
+        <v>106855</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6913,30 +6913,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>220103</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>485094</v>
+        <v>484759</v>
       </c>
       <c r="R59" t="n">
-        <v>6473498</v>
+        <v>6473331</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6975,12 +6975,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 18029-2022 artfynd.xlsx
+++ b/artfynd/A 18029-2022 artfynd.xlsx
@@ -3615,10 +3615,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118305311</v>
+        <v>118305342</v>
       </c>
       <c r="B28" t="n">
-        <v>105495</v>
+        <v>57993</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3627,25 +3627,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220785</v>
+        <v>103055</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>484912</v>
+        <v>485057</v>
       </c>
       <c r="R28" t="n">
-        <v>6473377</v>
+        <v>6473346</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118305355</v>
+        <v>118305364</v>
       </c>
       <c r="B29" t="n">
-        <v>100107</v>
+        <v>104853</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3737,21 +3737,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>484703</v>
+        <v>484966</v>
       </c>
       <c r="R29" t="n">
-        <v>6473370</v>
+        <v>6473283</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118305342</v>
+        <v>118305311</v>
       </c>
       <c r="B30" t="n">
-        <v>57993</v>
+        <v>105495</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3839,25 +3839,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103055</v>
+        <v>220785</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>485057</v>
+        <v>484912</v>
       </c>
       <c r="R30" t="n">
-        <v>6473346</v>
+        <v>6473377</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3901,12 +3901,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3933,10 +3933,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118305364</v>
+        <v>118305355</v>
       </c>
       <c r="B31" t="n">
-        <v>104853</v>
+        <v>100107</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3949,21 +3949,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>484966</v>
+        <v>484703</v>
       </c>
       <c r="R31" t="n">
-        <v>6473283</v>
+        <v>6473370</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4675,10 +4675,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118305339</v>
+        <v>118305322</v>
       </c>
       <c r="B38" t="n">
-        <v>57287</v>
+        <v>104853</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4691,21 +4691,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102119</v>
+        <v>221141</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>485081</v>
+        <v>484760</v>
       </c>
       <c r="R38" t="n">
-        <v>6473386</v>
+        <v>6473457</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118305319</v>
+        <v>118305339</v>
       </c>
       <c r="B39" t="n">
-        <v>106776</v>
+        <v>57287</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4793,30 +4793,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220079</v>
+        <v>102119</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>484611</v>
+        <v>485081</v>
       </c>
       <c r="R39" t="n">
-        <v>6473524</v>
+        <v>6473386</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4887,10 +4887,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118305322</v>
+        <v>118305319</v>
       </c>
       <c r="B40" t="n">
-        <v>104853</v>
+        <v>106776</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4899,30 +4899,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221141</v>
+        <v>220079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>484760</v>
+        <v>484611</v>
       </c>
       <c r="R40" t="n">
-        <v>6473457</v>
+        <v>6473524</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5099,10 +5099,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118305313</v>
+        <v>118305372</v>
       </c>
       <c r="B42" t="n">
-        <v>100107</v>
+        <v>104853</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5115,21 +5115,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>484918</v>
+        <v>485107</v>
       </c>
       <c r="R42" t="n">
-        <v>6473370</v>
+        <v>6473491</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5205,7 +5205,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118305381</v>
+        <v>118305313</v>
       </c>
       <c r="B43" t="n">
         <v>100107</v>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>485107</v>
+        <v>484918</v>
       </c>
       <c r="R43" t="n">
-        <v>6473466</v>
+        <v>6473370</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5279,12 +5279,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5311,10 +5311,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118305372</v>
+        <v>118305381</v>
       </c>
       <c r="B44" t="n">
-        <v>104853</v>
+        <v>100107</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5327,26 +5327,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5358,7 +5358,7 @@
         <v>485107</v>
       </c>
       <c r="R44" t="n">
-        <v>6473491</v>
+        <v>6473466</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118305359</v>
+        <v>118305332</v>
       </c>
       <c r="B54" t="n">
-        <v>100107</v>
+        <v>108505</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6383,30 +6383,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>220228</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6415,10 +6415,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>484799</v>
+        <v>484606</v>
       </c>
       <c r="R54" t="n">
-        <v>6473280</v>
+        <v>6473524</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6445,12 +6445,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6477,10 +6477,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118305332</v>
+        <v>118305359</v>
       </c>
       <c r="B55" t="n">
-        <v>108505</v>
+        <v>100107</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6489,30 +6489,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220228</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>484606</v>
+        <v>484799</v>
       </c>
       <c r="R55" t="n">
-        <v>6473524</v>
+        <v>6473280</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6689,10 +6689,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118305343</v>
+        <v>118305330</v>
       </c>
       <c r="B57" t="n">
-        <v>57933</v>
+        <v>106855</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6701,30 +6701,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103042</v>
+        <v>220103</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>485042</v>
+        <v>484759</v>
       </c>
       <c r="R57" t="n">
-        <v>6473338</v>
+        <v>6473331</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6795,10 +6795,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118305315</v>
+        <v>118305343</v>
       </c>
       <c r="B58" t="n">
-        <v>100107</v>
+        <v>57933</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6807,25 +6807,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>103042</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6839,10 +6839,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>484915</v>
+        <v>485042</v>
       </c>
       <c r="R58" t="n">
-        <v>6473291</v>
+        <v>6473338</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6901,10 +6901,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118305330</v>
+        <v>118305315</v>
       </c>
       <c r="B59" t="n">
-        <v>106855</v>
+        <v>100107</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6913,30 +6913,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220103</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>484759</v>
+        <v>484915</v>
       </c>
       <c r="R59" t="n">
-        <v>6473331</v>
+        <v>6473291</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6975,12 +6975,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 18029-2022 artfynd.xlsx
+++ b/artfynd/A 18029-2022 artfynd.xlsx
@@ -1919,10 +1919,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118305329</v>
+        <v>118305359</v>
       </c>
       <c r="B12" t="n">
-        <v>108505</v>
+        <v>100107</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1931,30 +1931,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220228</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484656</v>
+        <v>484799</v>
       </c>
       <c r="R12" t="n">
-        <v>6473428</v>
+        <v>6473280</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2025,7 +2025,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118305323</v>
+        <v>118305313</v>
       </c>
       <c r="B13" t="n">
         <v>100107</v>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484694</v>
+        <v>484918</v>
       </c>
       <c r="R13" t="n">
-        <v>6473459</v>
+        <v>6473370</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118305375</v>
+        <v>118305367</v>
       </c>
       <c r="B14" t="n">
-        <v>100107</v>
+        <v>104853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485094</v>
+        <v>485042</v>
       </c>
       <c r="R14" t="n">
-        <v>6473498</v>
+        <v>6473417</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118305380</v>
+        <v>118305362</v>
       </c>
       <c r="B15" t="n">
-        <v>104853</v>
+        <v>100107</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2253,26 +2253,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485114</v>
+        <v>484972</v>
       </c>
       <c r="R15" t="n">
-        <v>6473403</v>
+        <v>6473266</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2343,7 +2343,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118305360</v>
+        <v>118305380</v>
       </c>
       <c r="B16" t="n">
         <v>104853</v>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484788</v>
+        <v>485114</v>
       </c>
       <c r="R16" t="n">
-        <v>6473281</v>
+        <v>6473403</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118305326</v>
+        <v>118305377</v>
       </c>
       <c r="B17" t="n">
-        <v>104853</v>
+        <v>100107</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2465,26 +2465,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484805</v>
+        <v>485117</v>
       </c>
       <c r="R17" t="n">
-        <v>6473426</v>
+        <v>6473448</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2523,12 +2523,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2555,10 +2555,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118305369</v>
+        <v>118305335</v>
       </c>
       <c r="B18" t="n">
-        <v>100107</v>
+        <v>106855</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2567,30 +2567,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>220103</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485043</v>
+        <v>484733</v>
       </c>
       <c r="R18" t="n">
-        <v>6473421</v>
+        <v>6473319</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2629,12 +2629,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2767,7 +2767,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118305377</v>
+        <v>118305369</v>
       </c>
       <c r="B20" t="n">
         <v>100107</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>485117</v>
+        <v>485043</v>
       </c>
       <c r="R20" t="n">
-        <v>6473448</v>
+        <v>6473421</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2873,7 +2873,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118305363</v>
+        <v>118305355</v>
       </c>
       <c r="B21" t="n">
         <v>100107</v>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>484973</v>
+        <v>484703</v>
       </c>
       <c r="R21" t="n">
-        <v>6473286</v>
+        <v>6473370</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2979,10 +2979,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118305334</v>
+        <v>118305342</v>
       </c>
       <c r="B22" t="n">
-        <v>108505</v>
+        <v>57993</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2995,26 +2995,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220228</v>
+        <v>103055</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>484663</v>
+        <v>485057</v>
       </c>
       <c r="R22" t="n">
-        <v>6473423</v>
+        <v>6473346</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,12 +3053,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,10 +3085,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118305317</v>
+        <v>118305319</v>
       </c>
       <c r="B23" t="n">
-        <v>109963</v>
+        <v>106776</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3097,30 +3097,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>220079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>484848</v>
+        <v>484611</v>
       </c>
       <c r="R23" t="n">
-        <v>6473423</v>
+        <v>6473524</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3191,10 +3191,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118305336</v>
+        <v>118305311</v>
       </c>
       <c r="B24" t="n">
-        <v>106855</v>
+        <v>105495</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3203,30 +3203,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220103</v>
+        <v>220785</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>484729</v>
+        <v>484912</v>
       </c>
       <c r="R24" t="n">
-        <v>6473311</v>
+        <v>6473377</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3265,12 +3265,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3297,10 +3297,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118305361</v>
+        <v>118305351</v>
       </c>
       <c r="B25" t="n">
-        <v>100107</v>
+        <v>57623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3309,25 +3309,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>103008</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>484933</v>
+        <v>485011</v>
       </c>
       <c r="R25" t="n">
-        <v>6473262</v>
+        <v>6473395</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3371,12 +3371,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3403,10 +3403,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118305351</v>
+        <v>118305325</v>
       </c>
       <c r="B26" t="n">
-        <v>57623</v>
+        <v>104853</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3415,25 +3415,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103008</v>
+        <v>221141</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>485011</v>
+        <v>484794</v>
       </c>
       <c r="R26" t="n">
-        <v>6473395</v>
+        <v>6473389</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3509,10 +3509,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118305333</v>
+        <v>118305354</v>
       </c>
       <c r="B27" t="n">
-        <v>106776</v>
+        <v>94143</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3521,30 +3521,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220079</v>
+        <v>2779</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>484662</v>
+        <v>484620</v>
       </c>
       <c r="R27" t="n">
-        <v>6473426</v>
+        <v>6473484</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3583,12 +3583,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3615,10 +3615,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118305342</v>
+        <v>118305321</v>
       </c>
       <c r="B28" t="n">
-        <v>57993</v>
+        <v>109963</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3627,25 +3627,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103055</v>
+        <v>219711</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>485057</v>
+        <v>484640</v>
       </c>
       <c r="R28" t="n">
-        <v>6473346</v>
+        <v>6473534</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118305364</v>
+        <v>118305340</v>
       </c>
       <c r="B29" t="n">
-        <v>104853</v>
+        <v>106855</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3733,30 +3733,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221141</v>
+        <v>220103</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>484966</v>
+        <v>484688</v>
       </c>
       <c r="R29" t="n">
-        <v>6473283</v>
+        <v>6473379</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3795,12 +3795,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3827,10 +3827,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118305311</v>
+        <v>118305379</v>
       </c>
       <c r="B30" t="n">
-        <v>105495</v>
+        <v>104853</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3839,20 +3839,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220785</v>
+        <v>221141</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>484912</v>
+        <v>485111</v>
       </c>
       <c r="R30" t="n">
-        <v>6473377</v>
+        <v>6473414</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3901,12 +3901,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3933,10 +3933,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118305355</v>
+        <v>118305326</v>
       </c>
       <c r="B31" t="n">
-        <v>100107</v>
+        <v>104853</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3949,21 +3949,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>484703</v>
+        <v>484805</v>
       </c>
       <c r="R31" t="n">
-        <v>6473370</v>
+        <v>6473426</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4007,12 +4007,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4039,10 +4039,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118305340</v>
+        <v>118305332</v>
       </c>
       <c r="B32" t="n">
-        <v>106855</v>
+        <v>108505</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4055,26 +4055,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220103</v>
+        <v>220228</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>484688</v>
+        <v>484606</v>
       </c>
       <c r="R32" t="n">
-        <v>6473379</v>
+        <v>6473524</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4113,12 +4113,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4145,10 +4145,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118305368</v>
+        <v>118305375</v>
       </c>
       <c r="B33" t="n">
-        <v>57993</v>
+        <v>100107</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4157,25 +4157,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103055</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>485047</v>
+        <v>485094</v>
       </c>
       <c r="R33" t="n">
-        <v>6473424</v>
+        <v>6473498</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4251,10 +4251,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118305376</v>
+        <v>118305363</v>
       </c>
       <c r="B34" t="n">
-        <v>104853</v>
+        <v>100107</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485097</v>
+        <v>484973</v>
       </c>
       <c r="R34" t="n">
-        <v>6473479</v>
+        <v>6473286</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4357,10 +4357,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118305325</v>
+        <v>118305334</v>
       </c>
       <c r="B35" t="n">
-        <v>104853</v>
+        <v>108505</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4369,20 +4369,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221141</v>
+        <v>220228</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>484794</v>
+        <v>484663</v>
       </c>
       <c r="R35" t="n">
-        <v>6473389</v>
+        <v>6473423</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4431,12 +4431,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4463,10 +4463,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118305367</v>
+        <v>118305330</v>
       </c>
       <c r="B36" t="n">
-        <v>104853</v>
+        <v>106855</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4475,30 +4475,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221141</v>
+        <v>220103</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485042</v>
+        <v>484759</v>
       </c>
       <c r="R36" t="n">
-        <v>6473417</v>
+        <v>6473331</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4537,12 +4537,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4569,10 +4569,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118305320</v>
+        <v>118305374</v>
       </c>
       <c r="B37" t="n">
-        <v>109963</v>
+        <v>104853</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4585,16 +4585,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219711</v>
+        <v>221141</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>484737</v>
+        <v>485099</v>
       </c>
       <c r="R37" t="n">
-        <v>6473599</v>
+        <v>6473500</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4643,12 +4643,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4675,7 +4675,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118305322</v>
+        <v>118305376</v>
       </c>
       <c r="B38" t="n">
         <v>104853</v>
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>484760</v>
+        <v>485097</v>
       </c>
       <c r="R38" t="n">
-        <v>6473457</v>
+        <v>6473479</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4749,12 +4749,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4781,10 +4781,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118305339</v>
+        <v>118305373</v>
       </c>
       <c r="B39" t="n">
-        <v>57287</v>
+        <v>100107</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102119</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>485081</v>
+        <v>485104</v>
       </c>
       <c r="R39" t="n">
-        <v>6473386</v>
+        <v>6473496</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4887,10 +4887,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118305319</v>
+        <v>118305343</v>
       </c>
       <c r="B40" t="n">
-        <v>106776</v>
+        <v>57933</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4899,30 +4899,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220079</v>
+        <v>103042</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>484611</v>
+        <v>485042</v>
       </c>
       <c r="R40" t="n">
-        <v>6473524</v>
+        <v>6473338</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4961,12 +4961,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4993,10 +4993,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118305371</v>
+        <v>118305333</v>
       </c>
       <c r="B41" t="n">
-        <v>104853</v>
+        <v>106776</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5005,30 +5005,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221141</v>
+        <v>220079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>485082</v>
+        <v>484662</v>
       </c>
       <c r="R41" t="n">
-        <v>6473404</v>
+        <v>6473426</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5099,7 +5099,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118305372</v>
+        <v>118305360</v>
       </c>
       <c r="B42" t="n">
         <v>104853</v>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>485107</v>
+        <v>484788</v>
       </c>
       <c r="R42" t="n">
-        <v>6473491</v>
+        <v>6473281</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118305313</v>
+        <v>118305372</v>
       </c>
       <c r="B43" t="n">
-        <v>100107</v>
+        <v>104853</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5221,21 +5221,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>484918</v>
+        <v>485107</v>
       </c>
       <c r="R43" t="n">
-        <v>6473370</v>
+        <v>6473491</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5279,12 +5279,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5311,10 +5311,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118305381</v>
+        <v>118305318</v>
       </c>
       <c r="B44" t="n">
-        <v>100107</v>
+        <v>102758</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5327,26 +5327,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>485107</v>
+        <v>484764</v>
       </c>
       <c r="R44" t="n">
-        <v>6473466</v>
+        <v>6473594</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5385,12 +5385,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5417,10 +5417,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118305379</v>
+        <v>118305317</v>
       </c>
       <c r="B45" t="n">
-        <v>104853</v>
+        <v>109963</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5433,16 +5433,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221141</v>
+        <v>219711</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>485111</v>
+        <v>484848</v>
       </c>
       <c r="R45" t="n">
-        <v>6473414</v>
+        <v>6473423</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5523,10 +5523,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118305348</v>
+        <v>118305368</v>
       </c>
       <c r="B46" t="n">
-        <v>57933</v>
+        <v>57993</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5535,25 +5535,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103042</v>
+        <v>103055</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>484666</v>
+        <v>485047</v>
       </c>
       <c r="R46" t="n">
-        <v>6473631</v>
+        <v>6473424</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5597,12 +5597,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5629,7 +5629,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118305335</v>
+        <v>118305336</v>
       </c>
       <c r="B47" t="n">
         <v>106855</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>484733</v>
+        <v>484729</v>
       </c>
       <c r="R47" t="n">
-        <v>6473319</v>
+        <v>6473311</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118305373</v>
+        <v>118305364</v>
       </c>
       <c r="B48" t="n">
-        <v>100107</v>
+        <v>104853</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5751,21 +5751,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>485104</v>
+        <v>484966</v>
       </c>
       <c r="R48" t="n">
-        <v>6473496</v>
+        <v>6473283</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118305362</v>
+        <v>118305322</v>
       </c>
       <c r="B49" t="n">
-        <v>100107</v>
+        <v>104853</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5857,21 +5857,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>484972</v>
+        <v>484760</v>
       </c>
       <c r="R49" t="n">
-        <v>6473266</v>
+        <v>6473457</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5915,12 +5915,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5947,10 +5947,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118305318</v>
+        <v>118305378</v>
       </c>
       <c r="B50" t="n">
-        <v>102758</v>
+        <v>100107</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5963,21 +5963,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>484764</v>
+        <v>485117</v>
       </c>
       <c r="R50" t="n">
-        <v>6473594</v>
+        <v>6473432</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6021,12 +6021,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6053,7 +6053,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118305378</v>
+        <v>118305315</v>
       </c>
       <c r="B51" t="n">
         <v>100107</v>
@@ -6097,10 +6097,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>485117</v>
+        <v>484915</v>
       </c>
       <c r="R51" t="n">
-        <v>6473432</v>
+        <v>6473291</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6127,12 +6127,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6159,10 +6159,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118305374</v>
+        <v>118305323</v>
       </c>
       <c r="B52" t="n">
-        <v>104853</v>
+        <v>100107</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6175,21 +6175,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6203,10 +6203,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>485099</v>
+        <v>484694</v>
       </c>
       <c r="R52" t="n">
-        <v>6473500</v>
+        <v>6473459</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6233,12 +6233,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6265,10 +6265,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118305321</v>
+        <v>118305329</v>
       </c>
       <c r="B53" t="n">
-        <v>109963</v>
+        <v>108505</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6277,20 +6277,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219711</v>
+        <v>220228</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>484640</v>
+        <v>484656</v>
       </c>
       <c r="R53" t="n">
-        <v>6473534</v>
+        <v>6473428</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118305332</v>
+        <v>118305348</v>
       </c>
       <c r="B54" t="n">
-        <v>108505</v>
+        <v>57933</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6383,30 +6383,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220228</v>
+        <v>103042</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6415,10 +6415,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>484606</v>
+        <v>484666</v>
       </c>
       <c r="R54" t="n">
-        <v>6473524</v>
+        <v>6473631</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6445,12 +6445,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6477,10 +6477,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118305359</v>
+        <v>118305371</v>
       </c>
       <c r="B55" t="n">
-        <v>100107</v>
+        <v>104853</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6493,26 +6493,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>484799</v>
+        <v>485082</v>
       </c>
       <c r="R55" t="n">
-        <v>6473280</v>
+        <v>6473404</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6583,10 +6583,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118305354</v>
+        <v>118305381</v>
       </c>
       <c r="B56" t="n">
-        <v>94143</v>
+        <v>100107</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6599,26 +6599,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2779</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6627,10 +6627,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>484620</v>
+        <v>485107</v>
       </c>
       <c r="R56" t="n">
-        <v>6473484</v>
+        <v>6473466</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6689,10 +6689,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118305330</v>
+        <v>118305339</v>
       </c>
       <c r="B57" t="n">
-        <v>106855</v>
+        <v>57287</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6701,30 +6701,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220103</v>
+        <v>102119</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>484759</v>
+        <v>485081</v>
       </c>
       <c r="R57" t="n">
-        <v>6473331</v>
+        <v>6473386</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6795,10 +6795,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118305343</v>
+        <v>118305320</v>
       </c>
       <c r="B58" t="n">
-        <v>57933</v>
+        <v>109963</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6807,25 +6807,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103042</v>
+        <v>219711</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6839,10 +6839,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485042</v>
+        <v>484737</v>
       </c>
       <c r="R58" t="n">
-        <v>6473338</v>
+        <v>6473599</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6901,7 +6901,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118305315</v>
+        <v>118305361</v>
       </c>
       <c r="B59" t="n">
         <v>100107</v>
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>484915</v>
+        <v>484933</v>
       </c>
       <c r="R59" t="n">
-        <v>6473291</v>
+        <v>6473262</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6975,12 +6975,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 18029-2022 artfynd.xlsx
+++ b/artfynd/A 18029-2022 artfynd.xlsx
@@ -1919,10 +1919,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118305359</v>
+        <v>118305351</v>
       </c>
       <c r="B12" t="n">
-        <v>100107</v>
+        <v>57623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>103008</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484799</v>
+        <v>485011</v>
       </c>
       <c r="R12" t="n">
-        <v>6473280</v>
+        <v>6473395</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2025,10 +2025,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118305313</v>
+        <v>118305373</v>
       </c>
       <c r="B13" t="n">
-        <v>100107</v>
+        <v>100114</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484918</v>
+        <v>485104</v>
       </c>
       <c r="R13" t="n">
-        <v>6473370</v>
+        <v>6473496</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118305367</v>
+        <v>118305348</v>
       </c>
       <c r="B14" t="n">
-        <v>104853</v>
+        <v>57933</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221141</v>
+        <v>103042</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485042</v>
+        <v>484666</v>
       </c>
       <c r="R14" t="n">
-        <v>6473417</v>
+        <v>6473631</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2237,10 +2237,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118305362</v>
+        <v>118305325</v>
       </c>
       <c r="B15" t="n">
-        <v>100107</v>
+        <v>104860</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484972</v>
+        <v>484794</v>
       </c>
       <c r="R15" t="n">
-        <v>6473266</v>
+        <v>6473389</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2311,12 +2311,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2343,10 +2343,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118305380</v>
+        <v>118305364</v>
       </c>
       <c r="B16" t="n">
-        <v>104853</v>
+        <v>104860</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485114</v>
+        <v>484966</v>
       </c>
       <c r="R16" t="n">
-        <v>6473403</v>
+        <v>6473283</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118305377</v>
+        <v>118305342</v>
       </c>
       <c r="B17" t="n">
-        <v>100107</v>
+        <v>57993</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2461,30 +2461,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>103055</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485117</v>
+        <v>485057</v>
       </c>
       <c r="R17" t="n">
-        <v>6473448</v>
+        <v>6473346</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2523,12 +2523,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2555,10 +2555,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118305335</v>
+        <v>118305371</v>
       </c>
       <c r="B18" t="n">
-        <v>106855</v>
+        <v>104860</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2567,30 +2567,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220103</v>
+        <v>221141</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484733</v>
+        <v>485082</v>
       </c>
       <c r="R18" t="n">
-        <v>6473319</v>
+        <v>6473404</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2629,12 +2629,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2661,10 +2661,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118305366</v>
+        <v>118305361</v>
       </c>
       <c r="B19" t="n">
-        <v>100107</v>
+        <v>100114</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>485044</v>
+        <v>484933</v>
       </c>
       <c r="R19" t="n">
-        <v>6473454</v>
+        <v>6473262</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2767,10 +2767,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118305369</v>
+        <v>118305363</v>
       </c>
       <c r="B20" t="n">
-        <v>100107</v>
+        <v>100114</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>485043</v>
+        <v>484973</v>
       </c>
       <c r="R20" t="n">
-        <v>6473421</v>
+        <v>6473286</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118305355</v>
+        <v>118305333</v>
       </c>
       <c r="B21" t="n">
-        <v>100107</v>
+        <v>106783</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2885,30 +2885,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>220079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>484703</v>
+        <v>484662</v>
       </c>
       <c r="R21" t="n">
-        <v>6473370</v>
+        <v>6473426</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2947,12 +2947,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,10 +2979,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118305342</v>
+        <v>118305379</v>
       </c>
       <c r="B22" t="n">
-        <v>57993</v>
+        <v>104860</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,30 +2991,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103055</v>
+        <v>221141</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>485057</v>
+        <v>485111</v>
       </c>
       <c r="R22" t="n">
-        <v>6473346</v>
+        <v>6473414</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,12 +3053,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,10 +3085,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118305319</v>
+        <v>118305320</v>
       </c>
       <c r="B23" t="n">
-        <v>106776</v>
+        <v>109970</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3097,30 +3097,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220079</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>484611</v>
+        <v>484737</v>
       </c>
       <c r="R23" t="n">
-        <v>6473524</v>
+        <v>6473599</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3191,10 +3191,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118305311</v>
+        <v>118305362</v>
       </c>
       <c r="B24" t="n">
-        <v>105495</v>
+        <v>100114</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3203,25 +3203,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>484912</v>
+        <v>484972</v>
       </c>
       <c r="R24" t="n">
-        <v>6473377</v>
+        <v>6473266</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3265,12 +3265,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3297,10 +3297,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118305351</v>
+        <v>118305311</v>
       </c>
       <c r="B25" t="n">
-        <v>57623</v>
+        <v>105502</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3309,25 +3309,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103008</v>
+        <v>220785</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>485011</v>
+        <v>484912</v>
       </c>
       <c r="R25" t="n">
-        <v>6473395</v>
+        <v>6473377</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3371,12 +3371,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3403,10 +3403,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118305325</v>
+        <v>118305323</v>
       </c>
       <c r="B26" t="n">
-        <v>104853</v>
+        <v>100114</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>484794</v>
+        <v>484694</v>
       </c>
       <c r="R26" t="n">
-        <v>6473389</v>
+        <v>6473459</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118305354</v>
+        <v>118305315</v>
       </c>
       <c r="B27" t="n">
-        <v>94143</v>
+        <v>100114</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3525,21 +3525,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2779</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>484620</v>
+        <v>484915</v>
       </c>
       <c r="R27" t="n">
-        <v>6473484</v>
+        <v>6473291</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3583,12 +3583,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3615,10 +3615,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118305321</v>
+        <v>118305380</v>
       </c>
       <c r="B28" t="n">
-        <v>109963</v>
+        <v>104860</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3631,16 +3631,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219711</v>
+        <v>221141</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>484640</v>
+        <v>485114</v>
       </c>
       <c r="R28" t="n">
-        <v>6473534</v>
+        <v>6473403</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118305340</v>
+        <v>118305318</v>
       </c>
       <c r="B29" t="n">
-        <v>106855</v>
+        <v>102765</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3733,30 +3733,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220103</v>
+        <v>222002</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>484688</v>
+        <v>484764</v>
       </c>
       <c r="R29" t="n">
-        <v>6473379</v>
+        <v>6473594</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3795,12 +3795,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3827,10 +3827,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118305379</v>
+        <v>118305360</v>
       </c>
       <c r="B30" t="n">
-        <v>104853</v>
+        <v>104860</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>485111</v>
+        <v>484788</v>
       </c>
       <c r="R30" t="n">
-        <v>6473414</v>
+        <v>6473281</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3933,10 +3933,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118305326</v>
+        <v>118305335</v>
       </c>
       <c r="B31" t="n">
-        <v>104853</v>
+        <v>106862</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3945,30 +3945,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221141</v>
+        <v>220103</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>484805</v>
+        <v>484733</v>
       </c>
       <c r="R31" t="n">
-        <v>6473426</v>
+        <v>6473319</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4007,12 +4007,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4039,10 +4039,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118305332</v>
+        <v>118305334</v>
       </c>
       <c r="B32" t="n">
-        <v>108505</v>
+        <v>108512</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>484606</v>
+        <v>484663</v>
       </c>
       <c r="R32" t="n">
-        <v>6473524</v>
+        <v>6473423</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118305375</v>
+        <v>118305322</v>
       </c>
       <c r="B33" t="n">
-        <v>100107</v>
+        <v>104860</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>485094</v>
+        <v>484760</v>
       </c>
       <c r="R33" t="n">
-        <v>6473498</v>
+        <v>6473457</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4219,12 +4219,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4251,10 +4251,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118305363</v>
+        <v>118305381</v>
       </c>
       <c r="B34" t="n">
-        <v>100107</v>
+        <v>100114</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>484973</v>
+        <v>485107</v>
       </c>
       <c r="R34" t="n">
-        <v>6473286</v>
+        <v>6473466</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4357,10 +4357,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118305334</v>
+        <v>118305376</v>
       </c>
       <c r="B35" t="n">
-        <v>108505</v>
+        <v>104860</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4369,20 +4369,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220228</v>
+        <v>221141</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>484663</v>
+        <v>485097</v>
       </c>
       <c r="R35" t="n">
-        <v>6473423</v>
+        <v>6473479</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4431,12 +4431,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4463,10 +4463,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118305330</v>
+        <v>118305321</v>
       </c>
       <c r="B36" t="n">
-        <v>106855</v>
+        <v>109970</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4475,30 +4475,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220103</v>
+        <v>219711</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>484759</v>
+        <v>484640</v>
       </c>
       <c r="R36" t="n">
-        <v>6473331</v>
+        <v>6473534</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4569,10 +4569,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118305374</v>
+        <v>118305332</v>
       </c>
       <c r="B37" t="n">
-        <v>104853</v>
+        <v>108512</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4581,20 +4581,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221141</v>
+        <v>220228</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>485099</v>
+        <v>484606</v>
       </c>
       <c r="R37" t="n">
-        <v>6473500</v>
+        <v>6473524</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4643,12 +4643,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4675,10 +4675,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118305376</v>
+        <v>118305319</v>
       </c>
       <c r="B38" t="n">
-        <v>104853</v>
+        <v>106783</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4687,30 +4687,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221141</v>
+        <v>220079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4719,10 +4719,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>485097</v>
+        <v>484611</v>
       </c>
       <c r="R38" t="n">
-        <v>6473479</v>
+        <v>6473524</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4749,12 +4749,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4781,10 +4781,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118305373</v>
+        <v>118305374</v>
       </c>
       <c r="B39" t="n">
-        <v>100107</v>
+        <v>104860</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>485104</v>
+        <v>485099</v>
       </c>
       <c r="R39" t="n">
-        <v>6473496</v>
+        <v>6473500</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4887,10 +4887,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118305343</v>
+        <v>118305378</v>
       </c>
       <c r="B40" t="n">
-        <v>57933</v>
+        <v>100114</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4899,25 +4899,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103042</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>485042</v>
+        <v>485117</v>
       </c>
       <c r="R40" t="n">
-        <v>6473338</v>
+        <v>6473432</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4961,12 +4961,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4993,10 +4993,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118305333</v>
+        <v>118305368</v>
       </c>
       <c r="B41" t="n">
-        <v>106776</v>
+        <v>57993</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5009,26 +5009,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220079</v>
+        <v>103055</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>484662</v>
+        <v>485047</v>
       </c>
       <c r="R41" t="n">
-        <v>6473426</v>
+        <v>6473424</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5099,10 +5099,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118305360</v>
+        <v>118305355</v>
       </c>
       <c r="B42" t="n">
-        <v>104853</v>
+        <v>100114</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5115,21 +5115,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>484788</v>
+        <v>484703</v>
       </c>
       <c r="R42" t="n">
-        <v>6473281</v>
+        <v>6473370</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118305372</v>
+        <v>118305375</v>
       </c>
       <c r="B43" t="n">
-        <v>104853</v>
+        <v>100114</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5221,21 +5221,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>485107</v>
+        <v>485094</v>
       </c>
       <c r="R43" t="n">
-        <v>6473491</v>
+        <v>6473498</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118305318</v>
+        <v>118305354</v>
       </c>
       <c r="B44" t="n">
-        <v>102758</v>
+        <v>94150</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5327,21 +5327,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222002</v>
+        <v>2779</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>484764</v>
+        <v>484620</v>
       </c>
       <c r="R44" t="n">
-        <v>6473594</v>
+        <v>6473484</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5385,12 +5385,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5417,10 +5417,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118305317</v>
+        <v>118305340</v>
       </c>
       <c r="B45" t="n">
-        <v>109963</v>
+        <v>106862</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5429,30 +5429,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219711</v>
+        <v>220103</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>484848</v>
+        <v>484688</v>
       </c>
       <c r="R45" t="n">
-        <v>6473423</v>
+        <v>6473379</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5523,10 +5523,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118305368</v>
+        <v>118305369</v>
       </c>
       <c r="B46" t="n">
-        <v>57993</v>
+        <v>100114</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5535,25 +5535,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103055</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>485047</v>
+        <v>485043</v>
       </c>
       <c r="R46" t="n">
-        <v>6473424</v>
+        <v>6473421</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5629,10 +5629,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118305336</v>
+        <v>118305367</v>
       </c>
       <c r="B47" t="n">
-        <v>106855</v>
+        <v>104860</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5641,30 +5641,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220103</v>
+        <v>221141</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>484729</v>
+        <v>485042</v>
       </c>
       <c r="R47" t="n">
-        <v>6473311</v>
+        <v>6473417</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5703,12 +5703,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5735,10 +5735,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118305364</v>
+        <v>118305330</v>
       </c>
       <c r="B48" t="n">
-        <v>104853</v>
+        <v>106862</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5747,30 +5747,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221141</v>
+        <v>220103</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>484966</v>
+        <v>484759</v>
       </c>
       <c r="R48" t="n">
-        <v>6473283</v>
+        <v>6473331</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5841,10 +5841,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118305322</v>
+        <v>118305317</v>
       </c>
       <c r="B49" t="n">
-        <v>104853</v>
+        <v>109970</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5857,16 +5857,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221141</v>
+        <v>219711</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>484760</v>
+        <v>484848</v>
       </c>
       <c r="R49" t="n">
-        <v>6473457</v>
+        <v>6473423</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5947,10 +5947,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118305378</v>
+        <v>118305377</v>
       </c>
       <c r="B50" t="n">
-        <v>100107</v>
+        <v>100114</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5994,7 +5994,7 @@
         <v>485117</v>
       </c>
       <c r="R50" t="n">
-        <v>6473432</v>
+        <v>6473448</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6053,10 +6053,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118305315</v>
+        <v>118305313</v>
       </c>
       <c r="B51" t="n">
-        <v>100107</v>
+        <v>100114</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6097,10 +6097,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>484915</v>
+        <v>484918</v>
       </c>
       <c r="R51" t="n">
-        <v>6473291</v>
+        <v>6473370</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6159,10 +6159,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118305323</v>
+        <v>118305343</v>
       </c>
       <c r="B52" t="n">
-        <v>100107</v>
+        <v>57933</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6171,25 +6171,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>103042</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6203,10 +6203,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>484694</v>
+        <v>485042</v>
       </c>
       <c r="R52" t="n">
-        <v>6473459</v>
+        <v>6473338</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6233,12 +6233,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6265,10 +6265,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118305329</v>
+        <v>118305326</v>
       </c>
       <c r="B53" t="n">
-        <v>108505</v>
+        <v>104860</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6277,20 +6277,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220228</v>
+        <v>221141</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>484656</v>
+        <v>484805</v>
       </c>
       <c r="R53" t="n">
-        <v>6473428</v>
+        <v>6473426</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118305348</v>
+        <v>118305359</v>
       </c>
       <c r="B54" t="n">
-        <v>57933</v>
+        <v>100114</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6383,25 +6383,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103042</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6415,10 +6415,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>484666</v>
+        <v>484799</v>
       </c>
       <c r="R54" t="n">
-        <v>6473631</v>
+        <v>6473280</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6445,12 +6445,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6477,10 +6477,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118305371</v>
+        <v>118305339</v>
       </c>
       <c r="B55" t="n">
-        <v>104853</v>
+        <v>57287</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6493,26 +6493,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221141</v>
+        <v>102119</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>485082</v>
+        <v>485081</v>
       </c>
       <c r="R55" t="n">
-        <v>6473404</v>
+        <v>6473386</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6583,10 +6583,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118305381</v>
+        <v>118305366</v>
       </c>
       <c r="B56" t="n">
-        <v>100107</v>
+        <v>100114</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6627,10 +6627,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>485107</v>
+        <v>485044</v>
       </c>
       <c r="R56" t="n">
-        <v>6473466</v>
+        <v>6473454</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6689,10 +6689,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118305339</v>
+        <v>118305372</v>
       </c>
       <c r="B57" t="n">
-        <v>57287</v>
+        <v>104860</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6705,21 +6705,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102119</v>
+        <v>221141</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>485081</v>
+        <v>485107</v>
       </c>
       <c r="R57" t="n">
-        <v>6473386</v>
+        <v>6473491</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6795,10 +6795,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118305320</v>
+        <v>118305336</v>
       </c>
       <c r="B58" t="n">
-        <v>109963</v>
+        <v>106862</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6807,30 +6807,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219711</v>
+        <v>220103</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6839,10 +6839,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>484737</v>
+        <v>484729</v>
       </c>
       <c r="R58" t="n">
-        <v>6473599</v>
+        <v>6473311</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6901,10 +6901,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118305361</v>
+        <v>118305329</v>
       </c>
       <c r="B59" t="n">
-        <v>100107</v>
+        <v>108512</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6913,30 +6913,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>220228</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>484933</v>
+        <v>484656</v>
       </c>
       <c r="R59" t="n">
-        <v>6473262</v>
+        <v>6473428</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6975,12 +6975,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 18029-2022 artfynd.xlsx
+++ b/artfynd/A 18029-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7171068</v>
+        <v>118305354</v>
       </c>
       <c r="B2" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>2779</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Almlund 300 m SO Baggelycke, Ög</t>
+          <t>Grönlund, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484849.0177863543</v>
+        <v>484620</v>
       </c>
       <c r="R2" t="n">
-        <v>6473301.954537595</v>
+        <v>6473484</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1997-06-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1997-06-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre uppgifter om Östergötlands flora. Referens: Ekologiska Kunskapsgruppen Calluna, 2002. Naturvårdsprogram för Vadstena kommun, 272 s. Inlagda i Artportalen av Tommy Tyrberg.</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,69 +764,64 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Tyrberg</t>
+          <t>Valdemar Mejstad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Tommy Tyrberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Äldre fynd i Östergötlands flora</t>
-        </is>
-      </c>
+          <t>Valdemar Mejstad, Oscar Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7171069</v>
+        <v>118305339</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57942</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>102119</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Almlund 300 m SO Baggelycke, Ög</t>
+          <t>Grönlund, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484849.0177863543</v>
+        <v>485081</v>
       </c>
       <c r="R3" t="n">
-        <v>6473301.954537595</v>
+        <v>6473386</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,27 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1997-06-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1997-06-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre uppgifter om Östergötlands flora. Referens: Ekologiska Kunskapsgruppen Calluna, 2002. Naturvårdsprogram för Vadstena kommun, 272 s. Inlagda i Artportalen av Tommy Tyrberg.</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,31 +865,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Tyrberg</t>
+          <t>Valdemar Mejstad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Tommy Tyrberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Äldre fynd i Östergötlands flora</t>
-        </is>
-      </c>
+          <t>Valdemar Mejstad, Oscar Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7171072</v>
+        <v>118305351</v>
       </c>
       <c r="B4" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,37 +888,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>103008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Almlund 300 m SO Baggelycke, Ög</t>
+          <t>Grönlund, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484849.0177863543</v>
+        <v>485011</v>
       </c>
       <c r="R4" t="n">
-        <v>6473301.954537595</v>
+        <v>6473395</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,27 +946,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1997-06-04</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1997-06-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre uppgifter om Östergötlands flora. Referens: Ekologiska Kunskapsgruppen Calluna, 2002. Naturvårdsprogram för Vadstena kommun, 272 s. Inlagda i Artportalen av Tommy Tyrberg.</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,65 +966,64 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Tyrberg</t>
+          <t>Valdemar Mejstad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Tommy Tyrberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Äldre fynd i Östergötlands flora</t>
-        </is>
-      </c>
+          <t>Valdemar Mejstad, Oscar Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7171079</v>
+        <v>118305343</v>
       </c>
       <c r="B5" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>103042</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Almlund 300 m SO Baggelycke, Ög</t>
+          <t>Grönlund, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484849.0177863543</v>
+        <v>485042</v>
       </c>
       <c r="R5" t="n">
-        <v>6473301.954537595</v>
+        <v>6473338</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,27 +1047,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1997-06-04</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1997-06-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre uppgifter om Östergötlands flora. Referens: Ekologiska Kunskapsgruppen Calluna, 2002. Naturvårdsprogram för Vadstena kommun, 272 s. Inlagda i Artportalen av Tommy Tyrberg.</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,69 +1067,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Tyrberg</t>
+          <t>Valdemar Mejstad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Tommy Tyrberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Äldre fynd i Östergötlands flora</t>
-        </is>
-      </c>
+          <t>Valdemar Mejstad, Oscar Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7171070</v>
+        <v>118305348</v>
       </c>
       <c r="B6" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222002</v>
+        <v>103042</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Almlund 300 m SO Baggelycke, Ög</t>
+          <t>Grönlund, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484849.0177863543</v>
+        <v>484666</v>
       </c>
       <c r="R6" t="n">
-        <v>6473301.954537595</v>
+        <v>6473631</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,27 +1148,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1997-06-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1997-06-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre uppgifter om Östergötlands flora. Referens: Ekologiska Kunskapsgruppen Calluna, 2002. Naturvårdsprogram för Vadstena kommun, 272 s. Inlagda i Artportalen av Tommy Tyrberg.</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,69 +1168,64 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tommy Tyrberg</t>
+          <t>Valdemar Mejstad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Tommy Tyrberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Äldre fynd i Östergötlands flora</t>
-        </is>
-      </c>
+          <t>Valdemar Mejstad, Oscar Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7171078</v>
+        <v>118305342</v>
       </c>
       <c r="B7" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>103055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Almlund 300 m SO Baggelycke, Ög</t>
+          <t>Grönlund, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484849.0177863543</v>
+        <v>485057</v>
       </c>
       <c r="R7" t="n">
-        <v>6473301.954537595</v>
+        <v>6473346</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,27 +1249,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1997-06-04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1997-06-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre uppgifter om Östergötlands flora. Referens: Ekologiska Kunskapsgruppen Calluna, 2002. Naturvårdsprogram för Vadstena kommun, 272 s. Inlagda i Artportalen av Tommy Tyrberg.</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,77 +1269,64 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tommy Tyrberg</t>
+          <t>Valdemar Mejstad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Tommy Tyrberg</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Äldre fynd i Östergötlands flora</t>
-        </is>
-      </c>
+          <t>Valdemar Mejstad, Oscar Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102118023</v>
+        <v>118305368</v>
       </c>
       <c r="B8" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222002</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Baggelycke, 280 m O, Rogslösa kyrka, Ög</t>
+          <t>Grönlund, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484785.742886829</v>
+        <v>485047</v>
       </c>
       <c r="R8" t="n">
-        <v>6473503.966333824</v>
+        <v>6473424</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,27 +1350,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Med kleistogama blommor.</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,43 +1364,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Lundmiljö</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Adam Bergner</t>
+          <t>Valdemar Mejstad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Adam Bergner</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Projekt Östergötland Flora</t>
-        </is>
-      </c>
+          <t>Valdemar Mejstad, Oscar Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102118137</v>
+        <v>118305317</v>
       </c>
       <c r="B9" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,45 +1393,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220079</v>
+        <v>219711</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Baggelycke, 170 m NO, Rogslösa kyrka, Ög</t>
+          <t>Grönlund, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484605.5937369547</v>
+        <v>484848</v>
       </c>
       <c r="R9" t="n">
-        <v>6473621.530825247</v>
+        <v>6473423</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1610,22 +1451,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1634,81 +1465,70 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Igenväxande naturbetesmark</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Adam Bergner</t>
+          <t>Valdemar Mejstad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Adam Bergner</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Projekt Östergötland Flora</t>
-        </is>
-      </c>
+          <t>Valdemar Mejstad, Oscar Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102118313</v>
+        <v>118305320</v>
       </c>
       <c r="B10" t="n">
-        <v>100516</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>225046</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grönlund, 110 m NNV, Rogslösa kyrka, Ög</t>
+          <t>Grönlund, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484773.8305840945</v>
+        <v>484737</v>
       </c>
       <c r="R10" t="n">
-        <v>6473274.992488381</v>
+        <v>6473599</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1732,27 +1552,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ungplanta.</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1761,89 +1566,70 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Gles skog på näringsrik mark</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Adam Bergner</t>
+          <t>Valdemar Mejstad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Adam Bergner</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Projekt Östergötland Flora</t>
-        </is>
-      </c>
+          <t>Valdemar Mejstad, Oscar Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102118174</v>
+        <v>118305321</v>
       </c>
       <c r="B11" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Baggelycke, 280 m O, Rogslösa kyrka, Ög</t>
+          <t>Grönlund, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484785.742886829</v>
+        <v>484640</v>
       </c>
       <c r="R11" t="n">
-        <v>6473503.966333824</v>
+        <v>6473534</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1867,22 +1653,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1891,85 +1667,66 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Lundmiljö</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Adam Bergner</t>
+          <t>Valdemar Mejstad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Adam Bergner</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Projekt Östergötland Flora</t>
-        </is>
-      </c>
+          <t>Valdemar Mejstad, Oscar Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118305351</v>
+        <v>7171078</v>
       </c>
       <c r="B12" t="n">
-        <v>57623</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103008</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grönlund, Ög</t>
+          <t>Almlund 300 m SO Baggelycke, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485011</v>
+        <v>484849</v>
       </c>
       <c r="R12" t="n">
-        <v>6473395</v>
+        <v>6473302</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1993,12 +1750,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>1997-06-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>1997-06-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre uppgifter om Östergötlands flora. Referens: Ekologiska Kunskapsgruppen Calluna, 2002. Naturvårdsprogram för Vadstena kommun, 272 s. Inlagda i Artportalen av Tommy Tyrberg.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2013,69 +1775,72 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad</t>
+          <t>Tommy Tyrberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad, Oscar Ljunggren</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Via Tommy Tyrberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Äldre fynd i Östergötlands flora</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118305373</v>
+        <v>102118137</v>
       </c>
       <c r="B13" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>220079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grönlund, Ög</t>
+          <t>Baggelycke, 170 m NO, Rogslösa kyrka, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485104</v>
+        <v>484606</v>
       </c>
       <c r="R13" t="n">
-        <v>6473496</v>
+        <v>6473622</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2099,12 +1864,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2113,60 +1878,65 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Igenväxande naturbetesmark</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad</t>
+          <t>Adam Bergner</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad, Oscar Ljunggren</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Adam Bergner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Projekt Östergötland Flora</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118305348</v>
+        <v>118305319</v>
       </c>
       <c r="B14" t="n">
-        <v>57933</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103042</v>
+        <v>220079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2175,10 +1945,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484666</v>
+        <v>484611</v>
       </c>
       <c r="R14" t="n">
-        <v>6473631</v>
+        <v>6473524</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2205,12 +1975,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2237,42 +2007,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118305325</v>
+        <v>118305333</v>
       </c>
       <c r="B15" t="n">
-        <v>104860</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221141</v>
+        <v>220079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2281,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484794</v>
+        <v>484662</v>
       </c>
       <c r="R15" t="n">
-        <v>6473389</v>
+        <v>6473426</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2311,12 +2076,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2343,42 +2108,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118305364</v>
+        <v>118305330</v>
       </c>
       <c r="B16" t="n">
-        <v>104860</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221141</v>
+        <v>220103</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2387,10 +2147,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484966</v>
+        <v>484759</v>
       </c>
       <c r="R16" t="n">
-        <v>6473283</v>
+        <v>6473331</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2417,12 +2177,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2449,15 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118305342</v>
+        <v>118305335</v>
       </c>
       <c r="B17" t="n">
-        <v>57993</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,26 +2220,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103055</v>
+        <v>220103</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2493,10 +2248,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485057</v>
+        <v>484733</v>
       </c>
       <c r="R17" t="n">
-        <v>6473346</v>
+        <v>6473319</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2523,12 +2278,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2555,42 +2310,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118305371</v>
+        <v>118305336</v>
       </c>
       <c r="B18" t="n">
-        <v>104860</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221141</v>
+        <v>220103</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2599,10 +2349,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485082</v>
+        <v>484729</v>
       </c>
       <c r="R18" t="n">
-        <v>6473404</v>
+        <v>6473311</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2629,12 +2379,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2661,42 +2411,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118305361</v>
+        <v>118305340</v>
       </c>
       <c r="B19" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>220103</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2705,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>484933</v>
+        <v>484688</v>
       </c>
       <c r="R19" t="n">
-        <v>6473262</v>
+        <v>6473379</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2735,12 +2480,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2767,42 +2512,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118305363</v>
+        <v>118305329</v>
       </c>
       <c r="B20" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109866</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>220228</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2811,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>484973</v>
+        <v>484656</v>
       </c>
       <c r="R20" t="n">
-        <v>6473286</v>
+        <v>6473428</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2841,12 +2581,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,15 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118305333</v>
+        <v>118305332</v>
       </c>
       <c r="B21" t="n">
-        <v>106783</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109866</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2889,26 +2624,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220079</v>
+        <v>220228</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2917,10 +2652,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>484662</v>
+        <v>484606</v>
       </c>
       <c r="R21" t="n">
-        <v>6473426</v>
+        <v>6473524</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2979,32 +2714,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118305379</v>
+        <v>118305334</v>
       </c>
       <c r="B22" t="n">
-        <v>104860</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109866</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221141</v>
+        <v>220228</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3014,7 +2744,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3023,10 +2753,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>485111</v>
+        <v>484663</v>
       </c>
       <c r="R22" t="n">
-        <v>6473414</v>
+        <v>6473423</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,12 +2783,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,32 +2815,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118305320</v>
+        <v>118305311</v>
       </c>
       <c r="B23" t="n">
-        <v>109970</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219711</v>
+        <v>220785</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3129,10 +2854,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>484737</v>
+        <v>484912</v>
       </c>
       <c r="R23" t="n">
-        <v>6473599</v>
+        <v>6473377</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3159,12 +2884,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3191,15 +2916,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118305362</v>
+        <v>118305322</v>
       </c>
       <c r="B24" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3207,21 +2927,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3235,10 +2955,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>484972</v>
+        <v>484760</v>
       </c>
       <c r="R24" t="n">
-        <v>6473266</v>
+        <v>6473457</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3265,12 +2985,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3297,32 +3017,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118305311</v>
+        <v>118305325</v>
       </c>
       <c r="B25" t="n">
-        <v>105502</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220785</v>
+        <v>221141</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3341,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>484912</v>
+        <v>484794</v>
       </c>
       <c r="R25" t="n">
-        <v>6473377</v>
+        <v>6473389</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3371,12 +3086,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3403,15 +3118,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118305323</v>
+        <v>118305326</v>
       </c>
       <c r="B26" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3419,21 +3129,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3447,10 +3157,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>484694</v>
+        <v>484805</v>
       </c>
       <c r="R26" t="n">
-        <v>6473459</v>
+        <v>6473426</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3509,15 +3219,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118305315</v>
+        <v>118305360</v>
       </c>
       <c r="B27" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,21 +3230,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3553,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>484915</v>
+        <v>484788</v>
       </c>
       <c r="R27" t="n">
-        <v>6473291</v>
+        <v>6473281</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3583,12 +3288,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3615,15 +3320,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118305380</v>
+        <v>118305364</v>
       </c>
       <c r="B28" t="n">
-        <v>104860</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3650,7 +3350,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3659,10 +3359,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>485114</v>
+        <v>484966</v>
       </c>
       <c r="R28" t="n">
-        <v>6473403</v>
+        <v>6473283</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3721,15 +3421,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118305318</v>
+        <v>118305367</v>
       </c>
       <c r="B29" t="n">
-        <v>102765</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3737,16 +3432,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222002</v>
+        <v>221141</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3765,10 +3460,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>484764</v>
+        <v>485042</v>
       </c>
       <c r="R29" t="n">
-        <v>6473594</v>
+        <v>6473417</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3795,12 +3490,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3827,15 +3522,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118305360</v>
+        <v>118305371</v>
       </c>
       <c r="B30" t="n">
-        <v>104860</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3862,7 +3552,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3871,10 +3561,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>484788</v>
+        <v>485082</v>
       </c>
       <c r="R30" t="n">
-        <v>6473281</v>
+        <v>6473404</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3933,42 +3623,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118305335</v>
+        <v>118305372</v>
       </c>
       <c r="B31" t="n">
-        <v>106862</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220103</v>
+        <v>221141</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3977,10 +3662,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>484733</v>
+        <v>485107</v>
       </c>
       <c r="R31" t="n">
-        <v>6473319</v>
+        <v>6473491</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4007,12 +3692,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4039,32 +3724,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118305334</v>
+        <v>118305374</v>
       </c>
       <c r="B32" t="n">
-        <v>108512</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220228</v>
+        <v>221141</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4074,7 +3754,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4083,10 +3763,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>484663</v>
+        <v>485099</v>
       </c>
       <c r="R32" t="n">
-        <v>6473423</v>
+        <v>6473500</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4113,12 +3793,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4145,15 +3825,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118305322</v>
+        <v>118305376</v>
       </c>
       <c r="B33" t="n">
-        <v>104860</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4189,10 +3864,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>484760</v>
+        <v>485097</v>
       </c>
       <c r="R33" t="n">
-        <v>6473457</v>
+        <v>6473479</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4219,12 +3894,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4251,15 +3926,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118305381</v>
+        <v>118305379</v>
       </c>
       <c r="B34" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4267,26 +3937,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4295,10 +3965,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485107</v>
+        <v>485111</v>
       </c>
       <c r="R34" t="n">
-        <v>6473466</v>
+        <v>6473414</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4357,15 +4027,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118305376</v>
+        <v>118305380</v>
       </c>
       <c r="B35" t="n">
-        <v>104860</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,7 +4057,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4401,10 +4066,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485097</v>
+        <v>485114</v>
       </c>
       <c r="R35" t="n">
-        <v>6473479</v>
+        <v>6473403</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4463,15 +4128,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118305321</v>
+        <v>7171070</v>
       </c>
       <c r="B36" t="n">
-        <v>109970</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4479,16 +4139,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219711</v>
+        <v>222002</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4496,24 +4156,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Grönlund, Ög</t>
+          <t>Almlund 300 m SO Baggelycke, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>484640</v>
+        <v>484849</v>
       </c>
       <c r="R36" t="n">
-        <v>6473534</v>
+        <v>6473302</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4537,12 +4193,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>1997-06-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>1997-06-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre uppgifter om Östergötlands flora. Referens: Ekologiska Kunskapsgruppen Calluna, 2002. Naturvårdsprogram för Vadstena kommun, 272 s. Inlagda i Artportalen av Tommy Tyrberg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4557,44 +4218,43 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad</t>
+          <t>Tommy Tyrberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad, Oscar Ljunggren</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Via Tommy Tyrberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Äldre fynd i Östergötlands flora</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118305332</v>
+        <v>102118023</v>
       </c>
       <c r="B37" t="n">
-        <v>108512</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220228</v>
+        <v>222002</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4602,24 +4262,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Grönlund, Ög</t>
+          <t>Baggelycke, 280 m O, Rogslösa kyrka, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>484606</v>
+        <v>484786</v>
       </c>
       <c r="R37" t="n">
-        <v>6473524</v>
+        <v>6473504</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4643,12 +4307,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2022-06-28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Med kleistogama blommor.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4657,60 +4326,65 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Lundmiljö</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad</t>
+          <t>Adam Bergner</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad, Oscar Ljunggren</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Adam Bergner</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Projekt Östergötland Flora</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118305319</v>
+        <v>118305318</v>
       </c>
       <c r="B38" t="n">
-        <v>106783</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220079</v>
+        <v>222002</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4719,10 +4393,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>484611</v>
+        <v>484764</v>
       </c>
       <c r="R38" t="n">
-        <v>6473524</v>
+        <v>6473594</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4781,15 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118305374</v>
+        <v>7171069</v>
       </c>
       <c r="B39" t="n">
-        <v>104860</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4797,41 +4466,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Grönlund, Ög</t>
+          <t>Almlund 300 m SO Baggelycke, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>485099</v>
+        <v>484849</v>
       </c>
       <c r="R39" t="n">
-        <v>6473500</v>
+        <v>6473302</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4855,12 +4520,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>1997-06-04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>1997-06-04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre uppgifter om Östergötlands flora. Referens: Ekologiska Kunskapsgruppen Calluna, 2002. Naturvårdsprogram för Vadstena kommun, 272 s. Inlagda i Artportalen av Tommy Tyrberg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4875,27 +4545,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad</t>
+          <t>Tommy Tyrberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad, Oscar Ljunggren</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Via Tommy Tyrberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Äldre fynd i Östergötlands flora</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118305378</v>
+        <v>102118174</v>
       </c>
       <c r="B40" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4920,24 +4589,28 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Grönlund, Ög</t>
+          <t>Baggelycke, 280 m O, Rogslösa kyrka, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>485117</v>
+        <v>484786</v>
       </c>
       <c r="R40" t="n">
-        <v>6473432</v>
+        <v>6473504</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4961,12 +4634,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4975,55 +4648,60 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Lundmiljö</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad</t>
+          <t>Adam Bergner</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad, Oscar Ljunggren</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Adam Bergner</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Projekt Östergötland Flora</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118305368</v>
+        <v>118305313</v>
       </c>
       <c r="B41" t="n">
-        <v>57993</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103055</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5037,10 +4715,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>485047</v>
+        <v>484918</v>
       </c>
       <c r="R41" t="n">
-        <v>6473424</v>
+        <v>6473370</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5067,12 +4745,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5099,15 +4777,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118305355</v>
+        <v>118305315</v>
       </c>
       <c r="B42" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5143,10 +4816,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>484703</v>
+        <v>484915</v>
       </c>
       <c r="R42" t="n">
-        <v>6473370</v>
+        <v>6473291</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5173,12 +4846,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5205,15 +4878,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118305375</v>
+        <v>118305323</v>
       </c>
       <c r="B43" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5249,10 +4917,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>485094</v>
+        <v>484694</v>
       </c>
       <c r="R43" t="n">
-        <v>6473498</v>
+        <v>6473459</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5279,12 +4947,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5311,15 +4979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118305354</v>
+        <v>118305352</v>
       </c>
       <c r="B44" t="n">
-        <v>94150</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5327,21 +4990,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2779</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5355,10 +5018,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>484620</v>
+        <v>484691</v>
       </c>
       <c r="R44" t="n">
-        <v>6473484</v>
+        <v>6473673</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5417,42 +5080,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118305340</v>
+        <v>118305355</v>
       </c>
       <c r="B45" t="n">
-        <v>106862</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220103</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5461,10 +5119,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>484688</v>
+        <v>484703</v>
       </c>
       <c r="R45" t="n">
-        <v>6473379</v>
+        <v>6473370</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5491,12 +5149,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5523,15 +5181,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118305369</v>
+        <v>118305359</v>
       </c>
       <c r="B46" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5567,10 +5220,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>485043</v>
+        <v>484799</v>
       </c>
       <c r="R46" t="n">
-        <v>6473421</v>
+        <v>6473280</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5629,15 +5282,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118305367</v>
+        <v>118305361</v>
       </c>
       <c r="B47" t="n">
-        <v>104860</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5645,21 +5293,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5673,10 +5321,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>485042</v>
+        <v>484933</v>
       </c>
       <c r="R47" t="n">
-        <v>6473417</v>
+        <v>6473262</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5735,42 +5383,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118305330</v>
+        <v>118305362</v>
       </c>
       <c r="B48" t="n">
-        <v>106862</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220103</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5779,10 +5422,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>484759</v>
+        <v>484972</v>
       </c>
       <c r="R48" t="n">
-        <v>6473331</v>
+        <v>6473266</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5809,12 +5452,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5841,15 +5484,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118305317</v>
+        <v>118305363</v>
       </c>
       <c r="B49" t="n">
-        <v>109970</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5857,26 +5495,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5885,10 +5523,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>484848</v>
+        <v>484973</v>
       </c>
       <c r="R49" t="n">
-        <v>6473423</v>
+        <v>6473286</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5915,12 +5553,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5947,15 +5585,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118305377</v>
+        <v>118305366</v>
       </c>
       <c r="B50" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5982,7 +5615,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5991,10 +5624,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>485117</v>
+        <v>485044</v>
       </c>
       <c r="R50" t="n">
-        <v>6473448</v>
+        <v>6473454</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6053,15 +5686,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118305313</v>
+        <v>118305369</v>
       </c>
       <c r="B51" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6097,10 +5725,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>484918</v>
+        <v>485043</v>
       </c>
       <c r="R51" t="n">
-        <v>6473370</v>
+        <v>6473421</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6127,12 +5755,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6159,37 +5787,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118305343</v>
+        <v>118305373</v>
       </c>
       <c r="B52" t="n">
-        <v>57933</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103042</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6203,10 +5826,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>485042</v>
+        <v>485104</v>
       </c>
       <c r="R52" t="n">
-        <v>6473338</v>
+        <v>6473496</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6233,12 +5856,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6265,15 +5888,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118305326</v>
+        <v>118305375</v>
       </c>
       <c r="B53" t="n">
-        <v>104860</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6281,21 +5899,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6309,10 +5927,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>484805</v>
+        <v>485094</v>
       </c>
       <c r="R53" t="n">
-        <v>6473426</v>
+        <v>6473498</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6339,12 +5957,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6371,15 +5989,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118305359</v>
+        <v>118305377</v>
       </c>
       <c r="B54" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6406,7 +6019,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6415,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>484799</v>
+        <v>485117</v>
       </c>
       <c r="R54" t="n">
-        <v>6473280</v>
+        <v>6473448</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6477,15 +6090,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118305339</v>
+        <v>118305378</v>
       </c>
       <c r="B55" t="n">
-        <v>57287</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6493,21 +6101,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102119</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6521,10 +6129,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>485081</v>
+        <v>485117</v>
       </c>
       <c r="R55" t="n">
-        <v>6473386</v>
+        <v>6473432</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6551,12 +6159,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6583,15 +6191,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118305366</v>
+        <v>118305381</v>
       </c>
       <c r="B56" t="n">
-        <v>100114</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6618,7 +6221,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6627,10 +6230,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>485044</v>
+        <v>485107</v>
       </c>
       <c r="R56" t="n">
-        <v>6473454</v>
+        <v>6473466</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6689,15 +6292,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118305372</v>
+        <v>7171072</v>
       </c>
       <c r="B57" t="n">
-        <v>104860</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6705,16 +6303,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221141</v>
+        <v>222771</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6722,24 +6320,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Grönlund, Ög</t>
+          <t>Almlund 300 m SO Baggelycke, Ög</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>485107</v>
+        <v>484849</v>
       </c>
       <c r="R57" t="n">
-        <v>6473491</v>
+        <v>6473302</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6763,12 +6357,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>1997-06-04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>1997-06-04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre uppgifter om Östergötlands flora. Referens: Ekologiska Kunskapsgruppen Calluna, 2002. Naturvårdsprogram för Vadstena kommun, 272 s. Inlagda i Artportalen av Tommy Tyrberg.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6783,69 +6382,64 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad</t>
+          <t>Tommy Tyrberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad, Oscar Ljunggren</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Via Tommy Tyrberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Äldre fynd i Östergötlands flora</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118305336</v>
+        <v>7171068</v>
       </c>
       <c r="B58" t="n">
-        <v>106862</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220103</v>
+        <v>223246</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Grönlund, Ög</t>
+          <t>Almlund 300 m SO Baggelycke, Ög</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>484729</v>
+        <v>484849</v>
       </c>
       <c r="R58" t="n">
-        <v>6473311</v>
+        <v>6473302</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6869,12 +6463,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>1997-06-04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>1997-06-04</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre uppgifter om Östergötlands flora. Referens: Ekologiska Kunskapsgruppen Calluna, 2002. Naturvårdsprogram för Vadstena kommun, 272 s. Inlagda i Artportalen av Tommy Tyrberg.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6889,69 +6488,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad</t>
+          <t>Tommy Tyrberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad, Oscar Ljunggren</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Via Tommy Tyrberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Äldre fynd i Östergötlands flora</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118305329</v>
+        <v>7171079</v>
       </c>
       <c r="B59" t="n">
-        <v>108512</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220228</v>
+        <v>223597</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Grönlund, Ög</t>
+          <t>Almlund 300 m SO Baggelycke, Ög</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>484656</v>
+        <v>484849</v>
       </c>
       <c r="R59" t="n">
-        <v>6473428</v>
+        <v>6473302</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6975,12 +6565,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>1997-06-04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>1997-06-04</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Äldre uppgifter om Östergötlands flora. Referens: Ekologiska Kunskapsgruppen Calluna, 2002. Naturvårdsprogram för Vadstena kommun, 272 s. Inlagda i Artportalen av Tommy Tyrberg.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6995,15 +6590,131 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad</t>
+          <t>Tommy Tyrberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Valdemar Mejstad, Oscar Ljunggren</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
+          <t>Via Tommy Tyrberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Äldre fynd i Östergötlands flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>102118313</v>
+      </c>
+      <c r="B60" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Grönlund, 110 m NNV, Rogslösa kyrka, Ög</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>484774</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6473275</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Vadstena</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Rogslösa</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2022-06-28</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2022-06-28</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ungplanta.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Gles skog på näringsrik mark</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Adam Bergner</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Adam Bergner</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Projekt Östergötland Flora</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
